--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.86004825134181</v>
+        <v>11.83975784084304</v>
       </c>
       <c r="D2" t="n">
-        <v>72.8289335058185</v>
+        <v>11.83470169469551</v>
       </c>
       <c r="E2" t="n">
-        <v>1.010388379553603</v>
+        <v>0.1641881116774604</v>
       </c>
       <c r="F2" t="n">
-        <v>1.026304236678811</v>
+        <v>0.1667744384603065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.8392714922346</v>
+        <v>11.51138161748812</v>
       </c>
       <c r="D3" t="n">
-        <v>70.77632503246087</v>
+        <v>11.50115281777489</v>
       </c>
       <c r="E3" t="n">
-        <v>1.010388379553603</v>
+        <v>0.1641881116774604</v>
       </c>
       <c r="F3" t="n">
-        <v>1.026304236678811</v>
+        <v>0.1667744384603065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
